--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -671,16 +671,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>3.6043</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -741,7 +759,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>62.4</v>
+        <v>63.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -750,12 +768,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Adjudicated document, Fiscal (reported, Low to Medium confidence)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -765,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Reported general government debt, unverified; attributed to IMF Article IV, no report reference</t>
         </is>
       </c>
     </row>
@@ -958,12 +976,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -973,7 +991,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1258,6 +1276,16 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1268,7 +1296,9 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1276,7 +1306,9 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1284,7 +1316,9 @@
           <t>cpi_avg_pct</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1292,7 +1326,9 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1300,7 +1336,9 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1308,7 +1346,9 @@
           <t>primary_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1316,7 +1356,17 @@
           <t>gov_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" s="2" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Reported IMF Article IV figures per adjudicated document, unreferenced and unverified (Low to Medium), 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1324,7 +1374,9 @@
           <t>external_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1332,7 +1384,9 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1340,7 +1394,9 @@
           <t>revenue_pct_gdp</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1348,7 +1404,9 @@
           <t>interest_pct_revenue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document, Fiscal (reported, Low to Medium confidence)</t>
+          <t>Adjudicated document, fiscal section (attributed to IMF Article IV, no report reference, Low to Medium)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Reported general government debt, unverified; attributed to IMF Article IV, no report reference</t>
+          <t>Reported IMF Article IV figure, unreferenced, unverified; central government debt assumed</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reported IMF Article IV figures per adjudicated document, unreferenced and unverified (Low to Medium), 08-Oct-26</t>
+          <t>Adjudicated document, fiscal section, attributed to IMF Article IV without report reference (unverified), 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document, fiscal section (attributed to IMF Article IV, no report reference, Low to Medium)</t>
+          <t>Adjudicated document citing IMF Article IV (unreferenced, Low to Medium confidence)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Reported IMF Article IV figure, unreferenced, unverified; central government debt assumed</t>
+          <t>Reported government debt; unverified, attributed to IMF Article IV without report reference</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adjudicated document, fiscal section, attributed to IMF Article IV without report reference (unverified), 08-Oct-26</t>
+          <t>Adjudicated document citing IMF Article IV (unreferenced, unverified), 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adjudicated document citing IMF Article IV (unreferenced, Low to Medium confidence)</t>
+          <t>Adjudicated document 'Montenegro sovereign credit' (Low to Medium confidence)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Reported government debt; unverified, attributed to IMF Article IV without report reference</t>
+          <t>General government debt as reported; unverified, attributed to IMF Article IV without report reference</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adjudicated document citing IMF Article IV (unreferenced, unverified), 08-Oct-26</t>
+          <t>Adjudicated document 'Montenegro sovereign credit', 08-Oct-26; reported IMF Article IV figures, no report reference, unverified (Low to Medium)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Montenegro_Sovereign_Model.xlsx
+++ b/models/sovereigns/Montenegro_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/montenegro.json</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.6043</v>
+        <v>5.1904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
